--- a/ig/DM-AVRIL-2026/CodeSystem-TRE-R286-TypeFermeture.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-TRE-R286-TypeFermeture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251016120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-16T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,6 +97,9 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R286-TypeFermeture/FHIR/TRE-R286-TypeFermeture?vs</t>
+  </si>
+  <si>
     <t>Hierarchy</t>
   </si>
   <si>
@@ -118,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>6</t>
   </si>
   <si>
     <t>Code</t>
@@ -133,6 +136,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -142,34 +148,40 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
     <t>Date de fin d'exploitation d'un code concept</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>Statut d'un code concept</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
     <t>deprecationDate</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
   </si>
   <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
+    <t>Date de dépréciation du code</t>
   </si>
   <si>
     <t>retirementDate</t>
@@ -178,7 +190,28 @@
     <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
   </si>
   <si>
-    <t>Date Concept was retired</t>
+    <t>Date de retrait du code</t>
+  </si>
+  <si>
+    <t>TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes à inclure dans le JdvJ364TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>TypeFermetureEgeFiness</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#TypeFermetureEgeFiness</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes à inclure dans le JdvJ365TypeFermetureEgeFiness</t>
   </si>
   <si>
     <t>Level</t>
@@ -199,9 +232,6 @@
     <t>Définitive</t>
   </si>
   <si>
-    <t>Désigne la fermeture définitive d’un élément de l’organisation interne d’un établissement de santé</t>
-  </si>
-  <si>
     <t>ERR</t>
   </si>
   <si>
@@ -230,18 +260,6 @@
   </si>
   <si>
     <t>Provisoire</t>
-  </si>
-  <si>
-    <t>Désigne la fermeture provisoire d’un élément de l’organisation interne d’un établissement santé. L’utilisateur du référentiel ROR qui sélectionne cette valeur doit alors obligatoirement renseigner une date de réouverture de l’élément en question.</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>Prévisionnelle</t>
-  </si>
-  <si>
-    <t>Désigne la fermeture prévisionnelle d’un élément de l’organisation interne d’un établissement santé. L’utilisateur du référentiel ROR qui sélectionne cette valeur a alors la possibilité de renseigner une date de réouverture de l’élément en question.</t>
   </si>
 </sst>
 </file>
@@ -500,46 +518,48 @@
       <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -549,99 +569,133 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
       <c r="C3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -651,112 +705,94 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
